--- a/docs/Informe_Resultados_Defectos_TrazaDoc.xlsx
+++ b/docs/Informe_Resultados_Defectos_TrazaDoc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sofia\AppData\Local\Temp\claude\c--Users-sofia-OneDrive-Escritorio-Blockchain-Contratos\536b5854-6e74-4928-89b2-83d80b282f91\scratchpad\pps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F98AD7-A99A-4270-8F89-3D48152E00E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BBDA92-1503-4D80-8EC0-E9EED897F10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="217">
   <si>
     <t>Informe de resultados y defectos · TrazaDoc</t>
   </si>
@@ -101,7 +101,7 @@
     <t>Latencia de verificación, percentil 95 (ms)</t>
   </si>
   <si>
-    <t>tests/perf, ensayo del 15/10/2026</t>
+    <t>tests/perf, medición oficial del 27/10/2026</t>
   </si>
   <si>
     <t>3. Defectos</t>
@@ -113,7 +113,7 @@
     <t>Abiertos</t>
   </si>
   <si>
-    <t>Cerrados</t>
+    <t>Corregidos</t>
   </si>
   <si>
     <t>Crítica</t>
@@ -179,13 +179,214 @@
     <t>Defecto</t>
   </si>
   <si>
+    <t>Defectos y acciones correctivas</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Severidad</t>
+  </si>
+  <si>
+    <t>Prioridad</t>
+  </si>
+  <si>
+    <t>Acción correctiva</t>
+  </si>
+  <si>
+    <t>Responsable</t>
+  </si>
+  <si>
+    <t>DEF-01</t>
+  </si>
+  <si>
+    <t>La lista de contratos del Verificador no se actualiza después de verificar</t>
+  </si>
+  <si>
+    <t>CP-35</t>
+  </si>
+  <si>
+    <t>P3 Media</t>
+  </si>
+  <si>
+    <t>Nuevo</t>
+  </si>
+  <si>
+    <t>Recargar la lista de documentos después de cada verificación.</t>
+  </si>
+  <si>
+    <t>Laura Sofia Diaz Suarez</t>
+  </si>
+  <si>
+    <t>DEF-02</t>
+  </si>
+  <si>
+    <t>"Reenviar código" no envía un código nuevo</t>
+  </si>
+  <si>
+    <t>CP-03</t>
+  </si>
+  <si>
+    <t>P2 Alta</t>
+  </si>
+  <si>
+    <t>Hacer que el botón vuelva a pedir el código al servidor.</t>
+  </si>
+  <si>
+    <t>DEF-03</t>
+  </si>
+  <si>
+    <t>No se registran los intentos fallidos de inicio de sesión</t>
+  </si>
+  <si>
     <t>CP-11</t>
   </si>
   <si>
+    <t>Corregido</t>
+  </si>
+  <si>
+    <t>Guardar cada intento fallido (correo, fecha, hora y motivo, sin la contraseña).</t>
+  </si>
+  <si>
+    <t>Sofia Ortiz Daza</t>
+  </si>
+  <si>
+    <t>DEF-04</t>
+  </si>
+  <si>
+    <t>No existe la aceptación de la política de tratamiento de datos</t>
+  </si>
+  <si>
+    <t>CP-13 a CP-15</t>
+  </si>
+  <si>
+    <t>P1 Urgente</t>
+  </si>
+  <si>
+    <t>Mostrar la política en el primer ingreso y guardar su aceptación con versión y fecha.</t>
+  </si>
+  <si>
+    <t>Sofia y Laura</t>
+  </si>
+  <si>
+    <t>DEF-05</t>
+  </si>
+  <si>
+    <t>Los estados se muestran en minúscula</t>
+  </si>
+  <si>
+    <t>CP-22</t>
+  </si>
+  <si>
+    <t>P4 Baja</t>
+  </si>
+  <si>
+    <t>Mostrar los estados con mayúscula inicial.</t>
+  </si>
+  <si>
+    <t>DEF-06</t>
+  </si>
+  <si>
+    <t>Un Empleado puede consultar los datos de un documento ajeno</t>
+  </si>
+  <si>
+    <t>CP-29</t>
+  </si>
+  <si>
+    <t>Negar el acceso (403) a documentos de otros empleados.</t>
+  </si>
+  <si>
+    <t>Datos de ejecución (fuente de las fórmulas)</t>
+  </si>
+  <si>
+    <t>Copiados de docs/Pruebas_QA_QC_TrazaDoc.xlsx (hoja Casos de prueba). Para actualizar tras el Ciclo 2, pegar en la columna F el estado del Ciclo 2.</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Épica</t>
+  </si>
+  <si>
+    <t>Estado ciclo 1</t>
+  </si>
+  <si>
+    <t>Estado ciclo 2</t>
+  </si>
+  <si>
+    <t>Último resultado</t>
+  </si>
+  <si>
+    <t>CP-01</t>
+  </si>
+  <si>
+    <t>Funcional</t>
+  </si>
+  <si>
+    <t>Inicio de sesión con credenciales válidas</t>
+  </si>
+  <si>
+    <t>No ejecutado</t>
+  </si>
+  <si>
+    <t>CP-02</t>
+  </si>
+  <si>
+    <t>Inicio de sesión con credenciales inválidas</t>
+  </si>
+  <si>
+    <t>Código de verificación válido</t>
+  </si>
+  <si>
+    <t>CP-04</t>
+  </si>
+  <si>
+    <t>Acceso a un panel de otro rol</t>
+  </si>
+  <si>
+    <t>CP-05</t>
+  </si>
+  <si>
+    <t>Cierre de sesión</t>
+  </si>
+  <si>
+    <t>CP-06</t>
+  </si>
+  <si>
+    <t>Acceso después de cerrar sesión</t>
+  </si>
+  <si>
+    <t>CP-07</t>
+  </si>
+  <si>
+    <t>Cambio de contraseña correcto</t>
+  </si>
+  <si>
+    <t>CP-08</t>
+  </si>
+  <si>
+    <t>Cambio de contraseña con la actual errada</t>
+  </si>
+  <si>
+    <t>CP-09</t>
+  </si>
+  <si>
+    <t>Bloqueo tras 5 intentos fallidos</t>
+  </si>
+  <si>
+    <t>CP-10</t>
+  </si>
+  <si>
+    <t>Desbloqueo pasados 15 minutos</t>
+  </si>
+  <si>
     <t>Registro de intentos fallidos</t>
   </si>
   <si>
-    <t>DEF-03</t>
+    <t>CP-12</t>
+  </si>
+  <si>
+    <t>Cierre por inactividad</t>
   </si>
   <si>
     <t>CP-13</t>
@@ -194,9 +395,6 @@
     <t>Política de datos en el primer ingreso</t>
   </si>
   <si>
-    <t>DEF-04</t>
-  </si>
-  <si>
     <t>CP-14</t>
   </si>
   <si>
@@ -209,277 +407,82 @@
     <t>Acceso sin aceptar la política</t>
   </si>
   <si>
-    <t>CP-29</t>
+    <t>CP-16</t>
+  </si>
+  <si>
+    <t>Carga de un PDF válido de 10 MB</t>
+  </si>
+  <si>
+    <t>CP-17</t>
+  </si>
+  <si>
+    <t>Rechazo de DOCX o PDF de 25 MB</t>
+  </si>
+  <si>
+    <t>CP-18</t>
+  </si>
+  <si>
+    <t>Metadatos y huella automáticos</t>
+  </si>
+  <si>
+    <t>CP-19</t>
+  </si>
+  <si>
+    <t>La huella no cambia para el mismo contenido</t>
+  </si>
+  <si>
+    <t>CP-20</t>
+  </si>
+  <si>
+    <t>Registro en la blockchain con txID</t>
+  </si>
+  <si>
+    <t>CP-21</t>
+  </si>
+  <si>
+    <t>Falla de la red blockchain</t>
+  </si>
+  <si>
+    <t>Mis documentos muestra solo los propios</t>
+  </si>
+  <si>
+    <t>CP-23</t>
+  </si>
+  <si>
+    <t>Estado inicial Pendiente</t>
+  </si>
+  <si>
+    <t>CP-24</t>
+  </si>
+  <si>
+    <t>Trazabilidad de mis documentos</t>
+  </si>
+  <si>
+    <t>CP-25</t>
+  </si>
+  <si>
+    <t>Trazabilidad de un documento ajeno</t>
+  </si>
+  <si>
+    <t>CP-26</t>
+  </si>
+  <si>
+    <t>Selección de un documento registrado</t>
+  </si>
+  <si>
+    <t>CP-27</t>
+  </si>
+  <si>
+    <t>Identificador inexistente</t>
+  </si>
+  <si>
+    <t>CP-28</t>
+  </si>
+  <si>
+    <t>Huella completa para el Verificador</t>
   </si>
   <si>
     <t>Empleado sin acceso a la huella ajena</t>
-  </si>
-  <si>
-    <t>DEF-06</t>
-  </si>
-  <si>
-    <t>Defectos y acciones correctivas</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Severidad</t>
-  </si>
-  <si>
-    <t>Prioridad</t>
-  </si>
-  <si>
-    <t>Acción correctiva</t>
-  </si>
-  <si>
-    <t>Responsable</t>
-  </si>
-  <si>
-    <t>DEF-01</t>
-  </si>
-  <si>
-    <t>La lista de contratos del Verificador no se actualiza después de verificar</t>
-  </si>
-  <si>
-    <t>CP-35</t>
-  </si>
-  <si>
-    <t>P3 Media</t>
-  </si>
-  <si>
-    <t>Nuevo</t>
-  </si>
-  <si>
-    <t>Recargar la lista de documentos después de cada verificación.</t>
-  </si>
-  <si>
-    <t>Laura Sofia Diaz Suarez</t>
-  </si>
-  <si>
-    <t>DEF-02</t>
-  </si>
-  <si>
-    <t>"Reenviar código" no envía un código nuevo</t>
-  </si>
-  <si>
-    <t>CP-03</t>
-  </si>
-  <si>
-    <t>P2 Alta</t>
-  </si>
-  <si>
-    <t>Hacer que el botón vuelva a pedir el código al servidor.</t>
-  </si>
-  <si>
-    <t>No se registran los intentos fallidos de inicio de sesión</t>
-  </si>
-  <si>
-    <t>Guardar cada intento fallido (correo, fecha, hora y motivo, sin la contraseña).</t>
-  </si>
-  <si>
-    <t>Sofia Ortiz Daza</t>
-  </si>
-  <si>
-    <t>No existe la aceptación de la política de tratamiento de datos</t>
-  </si>
-  <si>
-    <t>CP-13 a CP-15</t>
-  </si>
-  <si>
-    <t>P1 Urgente</t>
-  </si>
-  <si>
-    <t>Mostrar la política en el primer ingreso y guardar su aceptación con versión y fecha.</t>
-  </si>
-  <si>
-    <t>Sofia y Laura</t>
-  </si>
-  <si>
-    <t>DEF-05</t>
-  </si>
-  <si>
-    <t>Los estados se muestran en minúscula</t>
-  </si>
-  <si>
-    <t>CP-22</t>
-  </si>
-  <si>
-    <t>P4 Baja</t>
-  </si>
-  <si>
-    <t>Mostrar los estados con mayúscula inicial.</t>
-  </si>
-  <si>
-    <t>Un Empleado puede consultar los datos de un documento ajeno</t>
-  </si>
-  <si>
-    <t>Negar el acceso (403) a documentos de otros empleados.</t>
-  </si>
-  <si>
-    <t>Datos de ejecución (fuente de las fórmulas)</t>
-  </si>
-  <si>
-    <t>Copiados de docs/Pruebas_QA_QC_TrazaDoc.xlsx (hoja Casos de prueba). Para actualizar tras el Ciclo 2, pegar en la columna F el estado del Ciclo 2.</t>
-  </si>
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Épica</t>
-  </si>
-  <si>
-    <t>Estado ciclo 1</t>
-  </si>
-  <si>
-    <t>Estado ciclo 2</t>
-  </si>
-  <si>
-    <t>Último resultado</t>
-  </si>
-  <si>
-    <t>CP-01</t>
-  </si>
-  <si>
-    <t>Funcional</t>
-  </si>
-  <si>
-    <t>Inicio de sesión con credenciales válidas</t>
-  </si>
-  <si>
-    <t>No ejecutado</t>
-  </si>
-  <si>
-    <t>CP-02</t>
-  </si>
-  <si>
-    <t>Inicio de sesión con credenciales inválidas</t>
-  </si>
-  <si>
-    <t>Código de verificación válido</t>
-  </si>
-  <si>
-    <t>CP-04</t>
-  </si>
-  <si>
-    <t>Acceso a un panel de otro rol</t>
-  </si>
-  <si>
-    <t>CP-05</t>
-  </si>
-  <si>
-    <t>Cierre de sesión</t>
-  </si>
-  <si>
-    <t>CP-06</t>
-  </si>
-  <si>
-    <t>Acceso después de cerrar sesión</t>
-  </si>
-  <si>
-    <t>CP-07</t>
-  </si>
-  <si>
-    <t>Cambio de contraseña correcto</t>
-  </si>
-  <si>
-    <t>CP-08</t>
-  </si>
-  <si>
-    <t>Cambio de contraseña con la actual errada</t>
-  </si>
-  <si>
-    <t>CP-09</t>
-  </si>
-  <si>
-    <t>Bloqueo tras 5 intentos fallidos</t>
-  </si>
-  <si>
-    <t>CP-10</t>
-  </si>
-  <si>
-    <t>Desbloqueo pasados 15 minutos</t>
-  </si>
-  <si>
-    <t>CP-12</t>
-  </si>
-  <si>
-    <t>Cierre por inactividad</t>
-  </si>
-  <si>
-    <t>CP-16</t>
-  </si>
-  <si>
-    <t>Carga de un PDF válido de 10 MB</t>
-  </si>
-  <si>
-    <t>CP-17</t>
-  </si>
-  <si>
-    <t>Rechazo de DOCX o PDF de 25 MB</t>
-  </si>
-  <si>
-    <t>CP-18</t>
-  </si>
-  <si>
-    <t>Metadatos y huella automáticos</t>
-  </si>
-  <si>
-    <t>CP-19</t>
-  </si>
-  <si>
-    <t>La huella no cambia para el mismo contenido</t>
-  </si>
-  <si>
-    <t>CP-20</t>
-  </si>
-  <si>
-    <t>Registro en la blockchain con txID</t>
-  </si>
-  <si>
-    <t>CP-21</t>
-  </si>
-  <si>
-    <t>Falla de la red blockchain</t>
-  </si>
-  <si>
-    <t>Mis documentos muestra solo los propios</t>
-  </si>
-  <si>
-    <t>CP-23</t>
-  </si>
-  <si>
-    <t>Estado inicial Pendiente</t>
-  </si>
-  <si>
-    <t>CP-24</t>
-  </si>
-  <si>
-    <t>Trazabilidad de mis documentos</t>
-  </si>
-  <si>
-    <t>CP-25</t>
-  </si>
-  <si>
-    <t>Trazabilidad de un documento ajeno</t>
-  </si>
-  <si>
-    <t>CP-26</t>
-  </si>
-  <si>
-    <t>Selección de un documento registrado</t>
-  </si>
-  <si>
-    <t>CP-27</t>
-  </si>
-  <si>
-    <t>Identificador inexistente</t>
-  </si>
-  <si>
-    <t>CP-28</t>
-  </si>
-  <si>
-    <t>Huella completa para el Verificador</t>
   </si>
   <si>
     <t>CP-30</t>
@@ -1236,7 +1239,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF(Datos!$G$5:$G$66,"PASS")</f>
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1245,7 +1248,7 @@
       </c>
       <c r="B8" s="5">
         <f>COUNTIF(Datos!$G$5:$G$66,"FAIL")</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1272,7 +1275,7 @@
       </c>
       <c r="B11" s="6">
         <f>IF(B6=0,0,B7/B6)</f>
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1295,7 +1298,7 @@
       </c>
       <c r="B14" s="6">
         <f>COUNTIFS(Datos!$B$5:$B$66,"Funcional",Datos!$G$5:$G$66,"PASS")/COUNTIF(Datos!$B$5:$B$66,"Funcional")</f>
-        <v>0.78431372549019607</v>
+        <v>0.88235294117647056</v>
       </c>
       <c r="C14" s="7">
         <v>0.9</v>
@@ -1344,12 +1347,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="12">
-        <v>2040</v>
+        <v>2059</v>
       </c>
       <c r="C17" s="13">
         <v>3000</v>
@@ -1389,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="5">
-        <f>COUNTIFS(Defectos!$D$4:$D$40,"Crítica",Defectos!$F$4:$F$40,"Cerrado")</f>
+        <f>COUNTIFS(Defectos!$D$4:$D$40,"Crítica",Defectos!$F$4:$F$40,"Corregido")+COUNTIFS(Defectos!$D$4:$D$40,"Crítica",Defectos!$F$4:$F$40,"Re-probado")+COUNTIFS(Defectos!$D$4:$D$40,"Crítica",Defectos!$F$4:$F$40,"Cerrado")</f>
         <v>0</v>
       </c>
     </row>
@@ -1403,11 +1406,11 @@
       </c>
       <c r="C21" s="5">
         <f>B21-D21</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="5">
+        <f>COUNTIFS(Defectos!$D$4:$D$40,"Alta",Defectos!$F$4:$F$40,"Corregido")+COUNTIFS(Defectos!$D$4:$D$40,"Alta",Defectos!$F$4:$F$40,"Re-probado")+COUNTIFS(Defectos!$D$4:$D$40,"Alta",Defectos!$F$4:$F$40,"Cerrado")</f>
         <v>1</v>
-      </c>
-      <c r="D21" s="5">
-        <f>COUNTIFS(Defectos!$D$4:$D$40,"Alta",Defectos!$F$4:$F$40,"Cerrado")</f>
-        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1420,11 +1423,11 @@
       </c>
       <c r="C22" s="5">
         <f>B22-D22</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" s="5">
-        <f>COUNTIFS(Defectos!$D$4:$D$40,"Media",Defectos!$F$4:$F$40,"Cerrado")</f>
-        <v>0</v>
+        <f>COUNTIFS(Defectos!$D$4:$D$40,"Media",Defectos!$F$4:$F$40,"Corregido")+COUNTIFS(Defectos!$D$4:$D$40,"Media",Defectos!$F$4:$F$40,"Re-probado")+COUNTIFS(Defectos!$D$4:$D$40,"Media",Defectos!$F$4:$F$40,"Cerrado")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1440,7 +1443,7 @@
         <v>2</v>
       </c>
       <c r="D23" s="5">
-        <f>COUNTIFS(Defectos!$D$4:$D$40,"Baja",Defectos!$F$4:$F$40,"Cerrado")</f>
+        <f>COUNTIFS(Defectos!$D$4:$D$40,"Baja",Defectos!$F$4:$F$40,"Corregido")+COUNTIFS(Defectos!$D$4:$D$40,"Baja",Defectos!$F$4:$F$40,"Re-probado")+COUNTIFS(Defectos!$D$4:$D$40,"Baja",Defectos!$F$4:$F$40,"Cerrado")</f>
         <v>0</v>
       </c>
     </row>
@@ -1454,11 +1457,11 @@
       </c>
       <c r="C24" s="15">
         <f>SUM(C20:C23)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D24" s="15">
         <f>SUM(D20:D23)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1473,7 +1476,7 @@
     <row r="27" spans="1:5" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="str">
         <f>"Se ejecutaron "&amp;B6&amp;" de "&amp;B5&amp;" casos de prueba ("&amp;TEXT(B10,"0%")&amp;"): "&amp;B7&amp;" aprobados y "&amp;B8&amp;" fallidos, para una tasa de aprobación de "&amp;TEXT(B11,"0%")&amp;"."</f>
-        <v>Se ejecutaron 50 de 62 casos de prueba (81%): 45 aprobados y 5 fallidos, para una tasa de aprobación de 90%.</v>
+        <v>Se ejecutaron 50 de 62 casos de prueba (81%): 50 aprobados y 0 fallidos, para una tasa de aprobación de 100%.</v>
       </c>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
@@ -1483,7 +1486,7 @@
     <row r="28" spans="1:5" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="str">
         <f>"Casos funcionales: "&amp;TEXT(B14,"0%")&amp;" aprobados frente a una meta de 90 % ("&amp;D14&amp;"). Integridad: "&amp;TEXT(B15,"0%")&amp;" de alteraciones detectadas con "&amp;B16&amp;" falsos positivos ("&amp;D15&amp;"). Latencia P95: "&amp;B17&amp;" ms frente a 3000 ms ("&amp;D17&amp;")."</f>
-        <v>Casos funcionales: 78% aprobados frente a una meta de 90 % (No cumple). Integridad: 100% de alteraciones detectadas con 0 falsos positivos (Cumple). Latencia P95: 2040 ms frente a 3000 ms (Cumple).</v>
+        <v>Casos funcionales: 88% aprobados frente a una meta de 90 % (No cumple). Integridad: 100% de alteraciones detectadas con 0 falsos positivos (Cumple). Latencia P95: 2059 ms frente a 3000 ms (Cumple).</v>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -1492,8 +1495,8 @@
     </row>
     <row r="29" spans="1:5" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="str">
-        <f>"Se registraron "&amp;B24&amp;" defectos (críticos: "&amp;B20&amp;", altos: "&amp;B21&amp;", medios: "&amp;B22&amp;", bajos: "&amp;B23&amp;"); "&amp;C24&amp;" siguen abiertos. Ninguno impide registrar ni verificar documentos."</f>
-        <v>Se registraron 6 defectos (críticos: 0, altos: 1, medios: 3, bajos: 2); 6 siguen abiertos. Ninguno impide registrar ni verificar documentos.</v>
+        <f>"Se registraron "&amp;B24&amp;" defectos (críticos: "&amp;B20&amp;", altos: "&amp;B21&amp;", medios: "&amp;B22&amp;", bajos: "&amp;B23&amp;"); "&amp;D24&amp;" corregidos y "&amp;C24&amp;" abiertos. Ninguno impide registrar ni verificar documentos."</f>
+        <v>Se registraron 6 defectos (críticos: 0, altos: 1, medios: 3, bajos: 2); 3 corregidos y 3 abiertos. Ninguno impide registrar ni verificar documentos.</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
@@ -1502,8 +1505,8 @@
     </row>
     <row r="30" spans="1:5" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="str">
-        <f>_xlfn._LONGTEXT("Los fallos se deben a dos requisitos aún sin implementar (aceptación de la política de datos y registro de intentos fallidos) y a un control de acceso de la API que deja ver datos de documentos ajenos. Las correcciones se priorizan por severidad y se vuel","ven a probar con regresión.")</f>
-        <v>Los fallos se deben a dos requisitos aún sin implementar (aceptación de la política de datos y registro de intentos fallidos) y a un control de acceso de la API que deja ver datos de documentos ajenos. Las correcciones se priorizan por severidad y se vuelven a probar con regresión.</v>
+        <f>IF(B8=0,_xlfn._LONGTEXT("No quedan casos fallidos: los tres defectos funcionales encontrados (aceptación de la política de datos, registro de intentos fallidos y acceso de un Empleado a documentos ajenos) se corrigieron y se volvieron a probar con regresión. Los casos sin ejecuta","r se completan en el Ciclo 2, en Azure."),"Los casos fallidos están asociados a los defectos abiertos de la hoja Defectos; las correcciones se priorizan por severidad y se vuelven a probar con regresión.")</f>
+        <v>No quedan casos fallidos: los tres defectos funcionales encontrados (aceptación de la política de datos, registro de intentos fallidos y acceso de un Empleado a documentos ajenos) se corrigieron y se volvieron a probar con regresión. Los casos sin ejecutar se completan en el Ciclo 2, en Azure.</v>
       </c>
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
@@ -1528,7 +1531,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -1572,11 +1575,11 @@
       </c>
       <c r="C4" s="5">
         <f>COUNTIFS(Datos!$C$5:$C$66,A4,Datos!$G$5:$G$66,"PASS")</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5">
         <f>COUNTIFS(Datos!$C$5:$C$66,A4,Datos!$G$5:$G$66,"FAIL")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" s="5">
         <f t="shared" ref="E4:E9" si="0">B4-C4-D4</f>
@@ -1584,7 +1587,7 @@
       </c>
       <c r="F4" s="10">
         <f t="shared" ref="F4:F10" si="1">IF(C4+D4=0,0,C4/(C4+D4))</f>
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1622,11 +1625,11 @@
       </c>
       <c r="C6" s="5">
         <f>COUNTIFS(Datos!$C$5:$C$66,A6,Datos!$G$5:$G$66,"PASS")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" s="5">
         <f>COUNTIFS(Datos!$C$5:$C$66,A6,Datos!$G$5:$G$66,"FAIL")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="5">
         <f t="shared" si="0"/>
@@ -1634,7 +1637,7 @@
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>0.92307692307692313</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1722,11 +1725,11 @@
       </c>
       <c r="C10" s="15">
         <f>SUM(C4:C9)</f>
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D10" s="15">
         <f>SUM(D4:D9)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E10" s="15">
         <f>SUM(E4:E9)</f>
@@ -1734,7 +1737,7 @@
       </c>
       <c r="F10" s="17">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1756,84 +1759,9 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
+  <mergeCells count="1">
     <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
@@ -1859,12 +1787,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>46</v>
@@ -1873,175 +1801,175 @@
         <v>44</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F6" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F9" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2068,55 +1996,55 @@
   <sheetData>
     <row r="1" spans="1:7" ht="126" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G5" s="4" t="str">
         <f t="shared" ref="G5:G36" si="0">IF(F5="No ejecutado",E5,F5)</f>
@@ -2125,22 +2053,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G6" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2149,22 +2077,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G7" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2173,22 +2101,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G8" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2197,22 +2125,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G9" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2221,22 +2149,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G10" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2245,22 +2173,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G11" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2269,22 +2197,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G12" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2293,22 +2221,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G13" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2317,22 +2245,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G14" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2341,46 +2269,46 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G15" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G16" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2389,74 +2317,74 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>50</v>
+        <v>117</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>51</v>
+        <v>118</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G17" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G18" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G19" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2464,7 +2392,7 @@
         <v>123</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>38</v>
@@ -2473,10 +2401,10 @@
         <v>124</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G20" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2488,7 +2416,7 @@
         <v>125</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>38</v>
@@ -2500,7 +2428,7 @@
         <v>34</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G21" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2512,7 +2440,7 @@
         <v>127</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>38</v>
@@ -2524,7 +2452,7 @@
         <v>34</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G22" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2536,7 +2464,7 @@
         <v>129</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>38</v>
@@ -2548,7 +2476,7 @@
         <v>34</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G23" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2560,7 +2488,7 @@
         <v>131</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>38</v>
@@ -2572,7 +2500,7 @@
         <v>34</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G24" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2584,7 +2512,7 @@
         <v>133</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>38</v>
@@ -2596,7 +2524,7 @@
         <v>34</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G25" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2605,10 +2533,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>38</v>
@@ -2620,7 +2548,7 @@
         <v>34</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G26" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2632,7 +2560,7 @@
         <v>136</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>38</v>
@@ -2644,7 +2572,7 @@
         <v>34</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G27" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2656,7 +2584,7 @@
         <v>138</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>38</v>
@@ -2668,7 +2596,7 @@
         <v>34</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G28" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2680,7 +2608,7 @@
         <v>140</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>38</v>
@@ -2692,7 +2620,7 @@
         <v>34</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G29" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2704,7 +2632,7 @@
         <v>142</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>39</v>
@@ -2716,7 +2644,7 @@
         <v>34</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G30" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2728,7 +2656,7 @@
         <v>144</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>39</v>
@@ -2740,7 +2668,7 @@
         <v>34</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G31" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2752,7 +2680,7 @@
         <v>146</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>39</v>
@@ -2764,7 +2692,7 @@
         <v>34</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G32" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2773,46 +2701,46 @@
     </row>
     <row r="33" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>58</v>
+        <v>148</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G33" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G34" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2821,22 +2749,22 @@
     </row>
     <row r="35" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G35" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2845,22 +2773,22 @@
     </row>
     <row r="36" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G36" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2869,22 +2797,22 @@
     </row>
     <row r="37" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G37" s="4" t="str">
         <f t="shared" ref="G37:G68" si="1">IF(F37="No ejecutado",E37,F37)</f>
@@ -2893,22 +2821,22 @@
     </row>
     <row r="38" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G38" s="4" t="str">
         <f t="shared" si="1"/>
@@ -2917,22 +2845,22 @@
     </row>
     <row r="39" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G39" s="4" t="str">
         <f t="shared" si="1"/>
@@ -2941,22 +2869,22 @@
     </row>
     <row r="40" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G40" s="4" t="str">
         <f t="shared" si="1"/>
@@ -2965,22 +2893,22 @@
     </row>
     <row r="41" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G41" s="4" t="str">
         <f t="shared" si="1"/>
@@ -2989,22 +2917,22 @@
     </row>
     <row r="42" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G42" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3013,22 +2941,22 @@
     </row>
     <row r="43" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F43" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G43" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3037,22 +2965,22 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F44" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G44" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3061,22 +2989,22 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G45" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3085,22 +3013,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F46" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G46" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3109,22 +3037,22 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G47" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3133,22 +3061,22 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F48" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G48" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3157,22 +3085,22 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G49" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3181,22 +3109,22 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G50" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3205,22 +3133,22 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G51" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3229,22 +3157,22 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F52" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G52" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3253,22 +3181,22 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G53" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3277,22 +3205,22 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>41</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F54" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G54" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3301,22 +3229,22 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>41</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F55" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G55" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3325,22 +3253,22 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F56" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G56" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3349,22 +3277,22 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G57" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3373,22 +3301,22 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F58" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G58" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3397,22 +3325,22 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F59" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G59" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3421,22 +3349,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F60" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G60" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3445,22 +3373,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F61" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G61" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3469,22 +3397,22 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F62" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G62" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3493,22 +3421,22 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F63" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G63" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3517,22 +3445,22 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F64" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G64" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3541,22 +3469,22 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F65" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G65" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3565,22 +3493,22 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F66" s="20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G66" s="4" t="str">
         <f t="shared" si="1"/>

--- a/docs/Informe_Resultados_Defectos_TrazaDoc.xlsx
+++ b/docs/Informe_Resultados_Defectos_TrazaDoc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sofia\AppData\Local\Temp\claude\c--Users-sofia-OneDrive-Escritorio-Blockchain-Contratos\536b5854-6e74-4928-89b2-83d80b282f91\scratchpad\pps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BBDA92-1503-4D80-8EC0-E9EED897F10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6218BB-4962-48EB-9458-3A73C3EEB30B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="219">
   <si>
     <t>Informe de resultados y defectos · TrazaDoc</t>
   </si>
@@ -89,19 +89,19 @@
     <t>Detección de alteraciones (20 documentos)</t>
   </si>
   <si>
-    <t>tests/integrity, 20/20 detectadas (25/10/2026)</t>
+    <t>tests/integrity en Azure, 20/20 detectadas (29/10/2026)</t>
   </si>
   <si>
     <t>Falsos positivos (originales marcados como alterados)</t>
   </si>
   <si>
-    <t>tests/integrity (25/10/2026)</t>
+    <t>tests/integrity en Azure (29/10/2026)</t>
   </si>
   <si>
     <t>Latencia de verificación, percentil 95 (ms)</t>
   </si>
   <si>
-    <t>tests/perf, medición oficial del 27/10/2026</t>
+    <t>tests/perf, Docker local (27/10/2026); en Azure P95 = 2125 ms con las 20 verificaciones de INT-01</t>
   </si>
   <si>
     <t>3. Defectos</t>
@@ -209,10 +209,10 @@
     <t>P3 Media</t>
   </si>
   <si>
-    <t>Nuevo</t>
-  </si>
-  <si>
-    <t>Recargar la lista de documentos después de cada verificación.</t>
+    <t>Cerrado</t>
+  </si>
+  <si>
+    <t>El backend responde Cache-Control: no-store y la pantalla recarga el listado en cada verificación nueva.</t>
   </si>
   <si>
     <t>Laura Sofia Diaz Suarez</t>
@@ -230,7 +230,7 @@
     <t>P2 Alta</t>
   </si>
   <si>
-    <t>Hacer que el botón vuelva a pedir el código al servidor.</t>
+    <t>Quitar el botón: no hay reenvío por diseño (C-09); si el código no llega, se inicia sesión de nuevo.</t>
   </si>
   <si>
     <t>DEF-03</t>
@@ -242,9 +242,6 @@
     <t>CP-11</t>
   </si>
   <si>
-    <t>Corregido</t>
-  </si>
-  <si>
     <t>Guardar cada intento fallido (correo, fecha, hora y motivo, sin la contraseña).</t>
   </si>
   <si>
@@ -296,10 +293,22 @@
     <t>Negar el acceso (403) a documentos de otros empleados.</t>
   </si>
   <si>
+    <t>DEF-07</t>
+  </si>
+  <si>
+    <t>Al cerrar sesión no aparece la pantalla "Sesión cerrada"</t>
+  </si>
+  <si>
+    <t>CP-05</t>
+  </si>
+  <si>
+    <t>Ir a la pantalla Sesión cerrada antes de cerrar la sesión, para que la ruta protegida no redirija al inicio.</t>
+  </si>
+  <si>
     <t>Datos de ejecución (fuente de las fórmulas)</t>
   </si>
   <si>
-    <t>Copiados de docs/Pruebas_QA_QC_TrazaDoc.xlsx (hoja Casos de prueba). Para actualizar tras el Ciclo 2, pegar en la columna F el estado del Ciclo 2.</t>
+    <t>Copiados de docs/Pruebas_QA_QC_TrazaDoc.xlsx (hoja Casos de prueba). Último resultado: el del Ciclo 2 (Azure) o, si el caso no se repitió allá, el del Ciclo 1.</t>
   </si>
   <si>
     <t>Tipo</t>
@@ -326,25 +335,22 @@
     <t>Inicio de sesión con credenciales válidas</t>
   </si>
   <si>
+    <t>CP-02</t>
+  </si>
+  <si>
+    <t>Inicio de sesión con credenciales inválidas</t>
+  </si>
+  <si>
+    <t>Código de verificación válido</t>
+  </si>
+  <si>
+    <t>CP-04</t>
+  </si>
+  <si>
+    <t>Acceso a un panel de otro rol</t>
+  </si>
+  <si>
     <t>No ejecutado</t>
-  </si>
-  <si>
-    <t>CP-02</t>
-  </si>
-  <si>
-    <t>Inicio de sesión con credenciales inválidas</t>
-  </si>
-  <si>
-    <t>Código de verificación válido</t>
-  </si>
-  <si>
-    <t>CP-04</t>
-  </si>
-  <si>
-    <t>Acceso a un panel de otro rol</t>
-  </si>
-  <si>
-    <t>CP-05</t>
   </si>
   <si>
     <t>Cierre de sesión</t>
@@ -1204,7 +1210,7 @@
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="str">
         <f>"Fuente de los resultados: "&amp;IF(COUNTIF(Datos!$F$5:$F$66,"No ejecutado")=62,"Ciclo 1, entorno local (11 al 25 de octubre de 2026). Ciclo 2 en Azure pendiente.","Último resultado de cada caso (Ciclo 2 en Azure cuando ya se ejecutó).")</f>
-        <v>Fuente de los resultados: Ciclo 1, entorno local (11 al 25 de octubre de 2026). Ciclo 2 en Azure pendiente.</v>
+        <v>Fuente de los resultados: Último resultado de cada caso (Ciclo 2 en Azure cuando ya se ejecutó).</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1230,7 +1236,7 @@
       </c>
       <c r="B6" s="5">
         <f>B7+B8</f>
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1239,7 +1245,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF(Datos!$G$5:$G$66,"PASS")</f>
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1257,7 +1263,7 @@
       </c>
       <c r="B9" s="5">
         <f>COUNTIF(Datos!$G$5:$G$66,"No ejecutado")+COUNTIF(Datos!$G$5:$G$66,"Bloqueado")</f>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1266,7 +1272,7 @@
       </c>
       <c r="B10" s="6">
         <f>IF(B5=0,0,B6/B5)</f>
-        <v>0.80645161290322576</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1298,14 +1304,14 @@
       </c>
       <c r="B14" s="6">
         <f>COUNTIFS(Datos!$B$5:$B$66,"Funcional",Datos!$G$5:$G$66,"PASS")/COUNTIF(Datos!$B$5:$B$66,"Funcional")</f>
-        <v>0.88235294117647056</v>
+        <v>1</v>
       </c>
       <c r="C14" s="7">
         <v>0.9</v>
       </c>
       <c r="D14" s="5" t="str">
         <f>IF(B14&gt;=C14,"Cumple","No cumple")</f>
-        <v>No cumple</v>
+        <v>Cumple</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>15</v>
@@ -1347,7 +1353,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>20</v>
       </c>
@@ -1423,11 +1429,11 @@
       </c>
       <c r="C22" s="5">
         <f>B22-D22</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="5">
         <f>COUNTIFS(Defectos!$D$4:$D$40,"Media",Defectos!$F$4:$F$40,"Corregido")+COUNTIFS(Defectos!$D$4:$D$40,"Media",Defectos!$F$4:$F$40,"Re-probado")+COUNTIFS(Defectos!$D$4:$D$40,"Media",Defectos!$F$4:$F$40,"Cerrado")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1436,15 +1442,15 @@
       </c>
       <c r="B23" s="5">
         <f>COUNTIF(Defectos!$D$4:$D$40,"Baja")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" s="5">
         <f>B23-D23</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23" s="5">
         <f>COUNTIFS(Defectos!$D$4:$D$40,"Baja",Defectos!$F$4:$F$40,"Corregido")+COUNTIFS(Defectos!$D$4:$D$40,"Baja",Defectos!$F$4:$F$40,"Re-probado")+COUNTIFS(Defectos!$D$4:$D$40,"Baja",Defectos!$F$4:$F$40,"Cerrado")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1453,15 +1459,15 @@
       </c>
       <c r="B24" s="15">
         <f>SUM(B20:B23)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C24" s="15">
         <f>SUM(C20:C23)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D24" s="15">
         <f>SUM(D20:D23)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1476,7 +1482,7 @@
     <row r="27" spans="1:5" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="str">
         <f>"Se ejecutaron "&amp;B6&amp;" de "&amp;B5&amp;" casos de prueba ("&amp;TEXT(B10,"0%")&amp;"): "&amp;B7&amp;" aprobados y "&amp;B8&amp;" fallidos, para una tasa de aprobación de "&amp;TEXT(B11,"0%")&amp;"."</f>
-        <v>Se ejecutaron 50 de 62 casos de prueba (81%): 50 aprobados y 0 fallidos, para una tasa de aprobación de 100%.</v>
+        <v>Se ejecutaron 62 de 62 casos de prueba (100%): 62 aprobados y 0 fallidos, para una tasa de aprobación de 100%.</v>
       </c>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
@@ -1486,7 +1492,7 @@
     <row r="28" spans="1:5" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="str">
         <f>"Casos funcionales: "&amp;TEXT(B14,"0%")&amp;" aprobados frente a una meta de 90 % ("&amp;D14&amp;"). Integridad: "&amp;TEXT(B15,"0%")&amp;" de alteraciones detectadas con "&amp;B16&amp;" falsos positivos ("&amp;D15&amp;"). Latencia P95: "&amp;B17&amp;" ms frente a 3000 ms ("&amp;D17&amp;")."</f>
-        <v>Casos funcionales: 88% aprobados frente a una meta de 90 % (No cumple). Integridad: 100% de alteraciones detectadas con 0 falsos positivos (Cumple). Latencia P95: 2059 ms frente a 3000 ms (Cumple).</v>
+        <v>Casos funcionales: 100% aprobados frente a una meta de 90 % (Cumple). Integridad: 100% de alteraciones detectadas con 0 falsos positivos (Cumple). Latencia P95: 2059 ms frente a 3000 ms (Cumple).</v>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -1496,7 +1502,7 @@
     <row r="29" spans="1:5" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="str">
         <f>"Se registraron "&amp;B24&amp;" defectos (críticos: "&amp;B20&amp;", altos: "&amp;B21&amp;", medios: "&amp;B22&amp;", bajos: "&amp;B23&amp;"); "&amp;D24&amp;" corregidos y "&amp;C24&amp;" abiertos. Ninguno impide registrar ni verificar documentos."</f>
-        <v>Se registraron 6 defectos (críticos: 0, altos: 1, medios: 3, bajos: 2); 3 corregidos y 3 abiertos. Ninguno impide registrar ni verificar documentos.</v>
+        <v>Se registraron 7 defectos (críticos: 0, altos: 1, medios: 3, bajos: 3); 7 corregidos y 0 abiertos. Ninguno impide registrar ni verificar documentos.</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
@@ -1505,8 +1511,8 @@
     </row>
     <row r="30" spans="1:5" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="str">
-        <f>IF(B8=0,_xlfn._LONGTEXT("No quedan casos fallidos: los tres defectos funcionales encontrados (aceptación de la política de datos, registro de intentos fallidos y acceso de un Empleado a documentos ajenos) se corrigieron y se volvieron a probar con regresión. Los casos sin ejecuta","r se completan en el Ciclo 2, en Azure."),"Los casos fallidos están asociados a los defectos abiertos de la hoja Defectos; las correcciones se priorizan por severidad y se vuelven a probar con regresión.")</f>
-        <v>No quedan casos fallidos: los tres defectos funcionales encontrados (aceptación de la política de datos, registro de intentos fallidos y acceso de un Empleado a documentos ajenos) se corrigieron y se volvieron a probar con regresión. Los casos sin ejecutar se completan en el Ciclo 2, en Azure.</v>
+        <f>IF(B8=0,_xlfn._LONGTEXT("No quedan casos fallidos: los tres defectos funcionales encontrados (aceptación de la política de datos, registro de intentos fallidos y acceso de un Empleado a documentos ajenos) se corrigieron y se volvieron a probar con regresión. Los siete defectos re","gistrados quedaron cerrados después de las re-pruebas del Ciclo 3."),"Los casos fallidos están asociados a los defectos abiertos de la hoja Defectos; las correcciones se priorizan por severidad y se vuelven a probar con regresión.")</f>
+        <v>No quedan casos fallidos: los tres defectos funcionales encontrados (aceptación de la política de datos, registro de intentos fallidos y acceso de un Empleado a documentos ajenos) se corrigieron y se volvieron a probar con regresión. Los siete defectos registrados quedaron cerrados después de las re-pruebas del Ciclo 3.</v>
       </c>
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
@@ -1575,7 +1581,7 @@
       </c>
       <c r="C4" s="5">
         <f>COUNTIFS(Datos!$C$5:$C$66,A4,Datos!$G$5:$G$66,"PASS")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="5">
         <f>COUNTIFS(Datos!$C$5:$C$66,A4,Datos!$G$5:$G$66,"FAIL")</f>
@@ -1583,7 +1589,7 @@
       </c>
       <c r="E4" s="5">
         <f t="shared" ref="E4:E9" si="0">B4-C4-D4</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="10">
         <f t="shared" ref="F4:F10" si="1">IF(C4+D4=0,0,C4/(C4+D4))</f>
@@ -1600,7 +1606,7 @@
       </c>
       <c r="C5" s="5">
         <f>COUNTIFS(Datos!$C$5:$C$66,A5,Datos!$G$5:$G$66,"PASS")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5">
         <f>COUNTIFS(Datos!$C$5:$C$66,A5,Datos!$G$5:$G$66,"FAIL")</f>
@@ -1608,7 +1614,7 @@
       </c>
       <c r="E5" s="5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" si="1"/>
@@ -1625,7 +1631,7 @@
       </c>
       <c r="C6" s="5">
         <f>COUNTIFS(Datos!$C$5:$C$66,A6,Datos!$G$5:$G$66,"PASS")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="5">
         <f>COUNTIFS(Datos!$C$5:$C$66,A6,Datos!$G$5:$G$66,"FAIL")</f>
@@ -1633,7 +1639,7 @@
       </c>
       <c r="E6" s="5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
@@ -1650,7 +1656,7 @@
       </c>
       <c r="C7" s="5">
         <f>COUNTIFS(Datos!$C$5:$C$66,A7,Datos!$G$5:$G$66,"PASS")</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D7" s="5">
         <f>COUNTIFS(Datos!$C$5:$C$66,A7,Datos!$G$5:$G$66,"FAIL")</f>
@@ -1658,7 +1664,7 @@
       </c>
       <c r="E7" s="5">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
@@ -1700,7 +1706,7 @@
       </c>
       <c r="C9" s="5">
         <f>COUNTIFS(Datos!$C$5:$C$66,A9,Datos!$G$5:$G$66,"PASS")</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D9" s="5">
         <f>COUNTIFS(Datos!$C$5:$C$66,A9,Datos!$G$5:$G$66,"FAIL")</f>
@@ -1708,7 +1714,7 @@
       </c>
       <c r="E9" s="5">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F9" s="10">
         <f t="shared" si="1"/>
@@ -1725,7 +1731,7 @@
       </c>
       <c r="C10" s="15">
         <f>SUM(C4:C9)</f>
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D10" s="15">
         <f>SUM(D4:D9)</f>
@@ -1733,7 +1739,7 @@
       </c>
       <c r="E10" s="15">
         <f>SUM(E4:E9)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F10" s="17">
         <f t="shared" si="1"/>
@@ -1773,7 +1779,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -1885,62 +1891,62 @@
         <v>63</v>
       </c>
       <c r="F6" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>73</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>79</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>57</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>59</v>
@@ -1948,13 +1954,13 @@
     </row>
     <row r="9" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>28</v>
@@ -1963,13 +1969,39 @@
         <v>63</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G9" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>70</v>
+      <c r="B10" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1996,12 +2028,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="126" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2009,42 +2041,42 @@
         <v>48</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G5" s="4" t="str">
         <f t="shared" ref="G5:G36" si="0">IF(F5="No ejecutado",E5,F5)</f>
@@ -2053,22 +2085,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G6" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2080,19 +2112,19 @@
         <v>62</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G7" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2101,46 +2133,46 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G8" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>No ejecutado</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G9" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2149,22 +2181,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G10" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2173,22 +2205,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G11" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2197,22 +2229,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G12" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2221,22 +2253,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G13" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2245,22 +2277,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G14" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2272,19 +2304,19 @@
         <v>67</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G15" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2293,22 +2325,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G16" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2317,22 +2349,22 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G17" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2341,22 +2373,22 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G18" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2365,22 +2397,22 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G19" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2389,46 +2421,46 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G20" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>No ejecutado</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G21" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2437,22 +2469,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G22" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2461,22 +2493,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G23" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2485,22 +2517,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G24" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2509,22 +2541,22 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G25" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2533,22 +2565,22 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G26" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2557,22 +2589,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G27" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2581,22 +2613,22 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G28" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2605,22 +2637,22 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G29" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2629,22 +2661,22 @@
     </row>
     <row r="30" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G30" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2653,22 +2685,22 @@
     </row>
     <row r="31" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G31" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2677,22 +2709,22 @@
     </row>
     <row r="32" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G32" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2701,22 +2733,22 @@
     </row>
     <row r="33" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G33" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2725,22 +2757,22 @@
     </row>
     <row r="34" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G34" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2749,46 +2781,46 @@
     </row>
     <row r="35" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G35" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>No ejecutado</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G36" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2797,22 +2829,22 @@
     </row>
     <row r="37" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G37" s="4" t="str">
         <f t="shared" ref="G37:G68" si="1">IF(F37="No ejecutado",E37,F37)</f>
@@ -2821,22 +2853,22 @@
     </row>
     <row r="38" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G38" s="4" t="str">
         <f t="shared" si="1"/>
@@ -2848,19 +2880,19 @@
         <v>55</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G39" s="4" t="str">
         <f t="shared" si="1"/>
@@ -2869,22 +2901,22 @@
     </row>
     <row r="40" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G40" s="4" t="str">
         <f t="shared" si="1"/>
@@ -2893,22 +2925,22 @@
     </row>
     <row r="41" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G41" s="4" t="str">
         <f t="shared" si="1"/>
@@ -2917,22 +2949,22 @@
     </row>
     <row r="42" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G42" s="4" t="str">
         <f t="shared" si="1"/>
@@ -2941,22 +2973,22 @@
     </row>
     <row r="43" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F43" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G43" s="4" t="str">
         <f t="shared" si="1"/>
@@ -2965,22 +2997,22 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F44" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G44" s="4" t="str">
         <f t="shared" si="1"/>
@@ -2989,22 +3021,22 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G45" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3013,22 +3045,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F46" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G46" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3037,46 +3069,46 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G47" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>No ejecutado</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F48" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G48" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3085,22 +3117,22 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G49" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3109,22 +3141,22 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G50" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3133,22 +3165,22 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G51" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3157,70 +3189,70 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F52" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G52" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>No ejecutado</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G53" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>No ejecutado</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>41</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F54" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G54" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3229,22 +3261,22 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>41</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F55" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G55" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3253,22 +3285,22 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F56" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G56" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3277,22 +3309,22 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>195</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>193</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G57" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3301,118 +3333,118 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F58" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G58" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>No ejecutado</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F59" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G59" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>No ejecutado</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F60" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G60" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>No ejecutado</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F61" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G61" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>No ejecutado</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F62" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G62" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3421,70 +3453,70 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B63" s="4" t="s">
         <v>208</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>206</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F63" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G63" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>No ejecutado</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="F64" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G64" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>No ejecutado</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F65" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G65" s="4" t="str">
         <f t="shared" si="1"/>
@@ -3493,22 +3525,22 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B66" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>213</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F66" s="20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G66" s="4" t="str">
         <f t="shared" si="1"/>
